--- a/405/405-practical.xlsx
+++ b/405/405-practical.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="6"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
@@ -1226,8 +1226,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0">
-      <a:off x="0" y="0"/>
-      <a:ext cx="0" cy="0"/>
+      <a:off x="1152524" y="2749549"/>
+      <a:ext cx="4571999" cy="2695574"/>
     </a:xfrm>
   </c:spPr>
   <c:printSettings>
@@ -1420,16 +1420,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>295274</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>130175</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>542924</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>34924</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>111125</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>238124</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>15874</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1439,8 +1439,8 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0">
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
+        <a:off x="1152524" y="2749549"/>
+        <a:ext cx="4571999" cy="2695574"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -5071,19 +5071,19 @@
         <v>5</v>
       </c>
       <c r="I3" s="35">
-        <f t="shared" ref="I3:I12" si="19">AVERAGE(C3:G3)</f>
+        <f>AVERAGE(C3:G3)</f>
         <v>52.799999999999997</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J12" si="20">MIN(C3:G3)</f>
+        <f>MIN(C3:G3)</f>
         <v>43</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K12" si="21">MAX(C3:G3)</f>
+        <f t="shared" ref="K3:K12" si="19">MAX(C3:G3)</f>
         <v>60</v>
       </c>
       <c r="L3">
-        <f t="shared" ref="L3:L12" si="22">K3-J3</f>
+        <f>K3-J3</f>
         <v>17</v>
       </c>
       <c r="M3">
@@ -5119,19 +5119,19 @@
         <v>5</v>
       </c>
       <c r="I4" s="35">
+        <f t="shared" ref="I4:I12" si="20">AVERAGE(C4:G4)</f>
+        <v>58.399999999999999</v>
+      </c>
+      <c r="J4">
+        <f t="shared" ref="J4:J12" si="21">MIN(C4:G4)</f>
+        <v>45</v>
+      </c>
+      <c r="K4">
         <f t="shared" si="19"/>
-        <v>58.399999999999999</v>
-      </c>
-      <c r="J4">
-        <f t="shared" si="20"/>
-        <v>45</v>
-      </c>
-      <c r="K4">
-        <f t="shared" si="21"/>
         <v>67</v>
       </c>
       <c r="L4">
-        <f t="shared" si="22"/>
+        <f t="shared" ref="L4:L12" si="22">K4-J4</f>
         <v>22</v>
       </c>
       <c r="M4">
@@ -5167,15 +5167,15 @@
         <v>5</v>
       </c>
       <c r="I5" s="35">
+        <f t="shared" si="20"/>
+        <v>61.399999999999999</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="21"/>
+        <v>40</v>
+      </c>
+      <c r="K5">
         <f t="shared" si="19"/>
-        <v>61.399999999999999</v>
-      </c>
-      <c r="J5">
-        <f t="shared" si="20"/>
-        <v>40</v>
-      </c>
-      <c r="K5">
-        <f t="shared" si="21"/>
         <v>78</v>
       </c>
       <c r="L5">
@@ -5215,15 +5215,15 @@
         <v>5</v>
       </c>
       <c r="I6" s="35">
+        <f t="shared" si="20"/>
+        <v>75</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="21"/>
+        <v>60</v>
+      </c>
+      <c r="K6">
         <f t="shared" si="19"/>
-        <v>75</v>
-      </c>
-      <c r="J6">
-        <f t="shared" si="20"/>
-        <v>60</v>
-      </c>
-      <c r="K6">
-        <f t="shared" si="21"/>
         <v>89</v>
       </c>
       <c r="L6">
@@ -5263,15 +5263,15 @@
         <v>5</v>
       </c>
       <c r="I7" s="35">
+        <f t="shared" si="20"/>
+        <v>51.799999999999997</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="21"/>
+        <v>38</v>
+      </c>
+      <c r="K7">
         <f t="shared" si="19"/>
-        <v>51.799999999999997</v>
-      </c>
-      <c r="J7">
-        <f t="shared" si="20"/>
-        <v>38</v>
-      </c>
-      <c r="K7">
-        <f t="shared" si="21"/>
         <v>70</v>
       </c>
       <c r="L7">
@@ -5311,15 +5311,15 @@
         <v>5</v>
       </c>
       <c r="I8" s="35">
+        <f t="shared" si="20"/>
+        <v>50.799999999999997</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="21"/>
+        <v>29</v>
+      </c>
+      <c r="K8">
         <f t="shared" si="19"/>
-        <v>50.799999999999997</v>
-      </c>
-      <c r="J8">
-        <f t="shared" si="20"/>
-        <v>29</v>
-      </c>
-      <c r="K8">
-        <f t="shared" si="21"/>
         <v>80</v>
       </c>
       <c r="L8">
@@ -5359,15 +5359,15 @@
         <v>5</v>
       </c>
       <c r="I9" s="35">
+        <f t="shared" si="20"/>
+        <v>60.799999999999997</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="21"/>
+        <v>30</v>
+      </c>
+      <c r="K9">
         <f t="shared" si="19"/>
-        <v>60.799999999999997</v>
-      </c>
-      <c r="J9">
-        <f t="shared" si="20"/>
-        <v>30</v>
-      </c>
-      <c r="K9">
-        <f t="shared" si="21"/>
         <v>80</v>
       </c>
       <c r="L9">
@@ -5407,15 +5407,15 @@
         <v>5</v>
       </c>
       <c r="I10" s="35">
+        <f t="shared" si="20"/>
+        <v>72.599999999999994</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="21"/>
+        <v>60</v>
+      </c>
+      <c r="K10">
         <f t="shared" si="19"/>
-        <v>72.599999999999994</v>
-      </c>
-      <c r="J10">
-        <f t="shared" si="20"/>
-        <v>60</v>
-      </c>
-      <c r="K10">
-        <f t="shared" si="21"/>
         <v>89</v>
       </c>
       <c r="L10">
@@ -5455,15 +5455,15 @@
         <v>5</v>
       </c>
       <c r="I11" s="35">
+        <f t="shared" si="20"/>
+        <v>62.200000000000003</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="21"/>
+        <v>48</v>
+      </c>
+      <c r="K11">
         <f t="shared" si="19"/>
-        <v>62.200000000000003</v>
-      </c>
-      <c r="J11">
-        <f t="shared" si="20"/>
-        <v>48</v>
-      </c>
-      <c r="K11">
-        <f t="shared" si="21"/>
         <v>79</v>
       </c>
       <c r="L11">
@@ -5503,15 +5503,15 @@
         <v>5</v>
       </c>
       <c r="I12" s="35">
+        <f t="shared" si="20"/>
+        <v>76</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="21"/>
+        <v>56</v>
+      </c>
+      <c r="K12">
         <f t="shared" si="19"/>
-        <v>76</v>
-      </c>
-      <c r="J12">
-        <f t="shared" si="20"/>
-        <v>56</v>
-      </c>
-      <c r="K12">
-        <f t="shared" si="21"/>
         <v>85</v>
       </c>
       <c r="L12">

--- a/405/405-practical.xlsx
+++ b/405/405-practical.xlsx
@@ -1,124 +1,125 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="8"/>
+    <workbookView xWindow="360" yWindow="15" windowWidth="18540" windowHeight="6495" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Answer Report 1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sensitivity Report 1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Limits Report 1" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Sheet3" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sheet4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Sheet5" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Sheet6" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Answer Report 1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sensitivity Report 1" sheetId="4" r:id="rId4"/>
+    <sheet name="Limits Report 1" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="6" r:id="rId6"/>
+    <sheet name="Sheet4" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet5" sheetId="8" r:id="rId8"/>
+    <sheet name="Sheet6" sheetId="9" r:id="rId9"/>
   </sheets>
   <definedNames>
+    <definedName name="solver_adj" localSheetId="5" hidden="1">Sheet3!$B$17:$C$17</definedName>
+    <definedName name="solver_adj" localSheetId="6" hidden="1">Sheet4!$C$5:$E$7</definedName>
+    <definedName name="solver_adj" localSheetId="7" hidden="1">Sheet5!$K$30:$N$32</definedName>
+    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
+    <definedName name="solver_cvg" localSheetId="7" hidden="1">0.0001</definedName>
+    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_drv" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_eng" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_est" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_itr" localSheetId="7" hidden="1">2147483647</definedName>
+    <definedName name="solver_lhs1" localSheetId="5" hidden="1">Sheet3!$D$21:$D$22</definedName>
+    <definedName name="solver_lhs1" localSheetId="6" hidden="1">Sheet4!$C$8:$E$8</definedName>
+    <definedName name="solver_lhs1" localSheetId="7" hidden="1">Sheet5!$K$33:$N$33</definedName>
+    <definedName name="solver_lhs2" localSheetId="5" hidden="1">Sheet3!$D$8</definedName>
+    <definedName name="solver_lhs2" localSheetId="6" hidden="1">Sheet4!$F$5:$F$7</definedName>
+    <definedName name="solver_lhs2" localSheetId="7" hidden="1">Sheet5!$O$30:$O$32</definedName>
+    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_mip" localSheetId="7" hidden="1">2147483647</definedName>
+    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
+    <definedName name="solver_mni" localSheetId="7" hidden="1">30</definedName>
+    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
+    <definedName name="solver_mrt" localSheetId="7" hidden="1">0.075</definedName>
+    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_msl" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_nod" localSheetId="7" hidden="1">2147483647</definedName>
+    <definedName name="solver_num" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_num" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_num" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_nwt" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_opt" localSheetId="5" hidden="1">Sheet3!$D$17</definedName>
+    <definedName name="solver_opt" localSheetId="6" hidden="1">Sheet4!$B$11</definedName>
+    <definedName name="solver_opt" localSheetId="7" hidden="1">Sheet5!$K$36</definedName>
+    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
+    <definedName name="solver_pre" localSheetId="7" hidden="1">0.000001</definedName>
+    <definedName name="solver_rbv" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_rbv" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
+    <definedName name="solver_rel1" localSheetId="7" hidden="1">3</definedName>
+    <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_rel2" localSheetId="7" hidden="1">1</definedName>
+    <definedName name="solver_rhs1" localSheetId="5" hidden="1">Sheet3!$F$21:$F$22</definedName>
+    <definedName name="solver_rhs1" localSheetId="6" hidden="1">Sheet4!$C$9:$E$9</definedName>
+    <definedName name="solver_rhs1" localSheetId="7" hidden="1">Sheet5!$K$34:$N$34</definedName>
+    <definedName name="solver_rhs2" localSheetId="5" hidden="1">Sheet3!$F$8</definedName>
+    <definedName name="solver_rhs2" localSheetId="6" hidden="1">Sheet4!$G$5:$G$7</definedName>
+    <definedName name="solver_rhs2" localSheetId="7" hidden="1">Sheet5!$P$30:$P$32</definedName>
+    <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_rlx" localSheetId="7" hidden="1">2</definedName>
+    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
+    <definedName name="solver_rsd" localSheetId="7" hidden="1">0</definedName>
+    <definedName name="solver_scl" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
+    <definedName name="solver_scl" localSheetId="7" hidden="1">1</definedName>
     <definedName name="solver_sho" localSheetId="4" hidden="1">2</definedName>
-    <definedName name="solver_adj" localSheetId="5" hidden="1">Sheet3!$B$17:$C$17</definedName>
-    <definedName name="solver_cvg" localSheetId="5" hidden="1">0.0001</definedName>
-    <definedName name="solver_drv" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_est" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_itr" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="5" hidden="1">Sheet3!$D$21:$D$22</definedName>
-    <definedName name="solver_lhs2" localSheetId="5" hidden="1">Sheet3!$D$8</definedName>
-    <definedName name="solver_mip" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_mni" localSheetId="5" hidden="1">30</definedName>
-    <definedName name="solver_mrt" localSheetId="5" hidden="1">0.075</definedName>
-    <definedName name="solver_msl" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_nod" localSheetId="5" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_nwt" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="5" hidden="1">Sheet3!$D$17</definedName>
-    <definedName name="solver_pre" localSheetId="5" hidden="1">0.000001</definedName>
-    <definedName name="solver_rbv" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_rel1" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_rel2" localSheetId="5" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="5" hidden="1">Sheet3!$F$21:$F$22</definedName>
-    <definedName name="solver_rhs2" localSheetId="5" hidden="1">Sheet3!$F$8</definedName>
-    <definedName name="solver_rlx" localSheetId="5" hidden="1">2</definedName>
-    <definedName name="solver_rsd" localSheetId="5" hidden="1">0</definedName>
-    <definedName name="solver_scl" localSheetId="5" hidden="1">2</definedName>
     <definedName name="solver_sho" localSheetId="5" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_sho" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_ssz" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
+    <definedName name="solver_ssz" localSheetId="7" hidden="1">100</definedName>
     <definedName name="solver_tim" localSheetId="5" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
+    <definedName name="solver_tim" localSheetId="7" hidden="1">2147483647</definedName>
     <definedName name="solver_tol" localSheetId="5" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
+    <definedName name="solver_tol" localSheetId="7" hidden="1">0.01</definedName>
     <definedName name="solver_typ" localSheetId="5" hidden="1">1</definedName>
+    <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="7" hidden="1">2</definedName>
     <definedName name="solver_val" localSheetId="5" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="7" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="5" hidden="1">3</definedName>
-    <definedName name="solver_adj" localSheetId="6" hidden="1">Sheet4!$C$5:$E$7</definedName>
-    <definedName name="solver_cvg" localSheetId="6" hidden="1">0.0001</definedName>
-    <definedName name="solver_drv" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_est" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_itr" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="6" hidden="1">Sheet4!$C$8:$E$8</definedName>
-    <definedName name="solver_lhs2" localSheetId="6" hidden="1">Sheet4!$F$5:$F$7</definedName>
-    <definedName name="solver_mip" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_mni" localSheetId="6" hidden="1">30</definedName>
-    <definedName name="solver_mrt" localSheetId="6" hidden="1">0.075</definedName>
-    <definedName name="solver_msl" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_nod" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_nwt" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="6" hidden="1">Sheet4!$B$11</definedName>
-    <definedName name="solver_pre" localSheetId="6" hidden="1">0.000001</definedName>
-    <definedName name="solver_rbv" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="6" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="6" hidden="1">Sheet4!$C$9:$E$9</definedName>
-    <definedName name="solver_rhs2" localSheetId="6" hidden="1">Sheet4!$G$5:$G$7</definedName>
-    <definedName name="solver_rlx" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_rsd" localSheetId="6" hidden="1">0</definedName>
-    <definedName name="solver_scl" localSheetId="6" hidden="1">1</definedName>
-    <definedName name="solver_sho" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_ssz" localSheetId="6" hidden="1">100</definedName>
-    <definedName name="solver_tim" localSheetId="6" hidden="1">2147483647</definedName>
-    <definedName name="solver_tol" localSheetId="6" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="6" hidden="1">2</definedName>
-    <definedName name="solver_val" localSheetId="6" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="6" hidden="1">3</definedName>
-    <definedName name="solver_adj" localSheetId="7" hidden="1">Sheet5!$K$30:$N$32</definedName>
-    <definedName name="solver_cvg" localSheetId="7" hidden="1">0.0001</definedName>
-    <definedName name="solver_drv" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_eng" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_est" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_itr" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_lhs1" localSheetId="7" hidden="1">Sheet5!$K$33:$N$33</definedName>
-    <definedName name="solver_lhs2" localSheetId="7" hidden="1">Sheet5!$O$30:$O$32</definedName>
-    <definedName name="solver_mip" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_mni" localSheetId="7" hidden="1">30</definedName>
-    <definedName name="solver_mrt" localSheetId="7" hidden="1">0.075</definedName>
-    <definedName name="solver_msl" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_neg" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_nod" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_num" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_nwt" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_opt" localSheetId="7" hidden="1">Sheet5!$K$36</definedName>
-    <definedName name="solver_pre" localSheetId="7" hidden="1">0.000001</definedName>
-    <definedName name="solver_rbv" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_rel1" localSheetId="7" hidden="1">3</definedName>
-    <definedName name="solver_rel2" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_rhs1" localSheetId="7" hidden="1">Sheet5!$K$34:$N$34</definedName>
-    <definedName name="solver_rhs2" localSheetId="7" hidden="1">Sheet5!$P$30:$P$32</definedName>
-    <definedName name="solver_rlx" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_rsd" localSheetId="7" hidden="1">0</definedName>
-    <definedName name="solver_scl" localSheetId="7" hidden="1">1</definedName>
-    <definedName name="solver_sho" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_ssz" localSheetId="7" hidden="1">100</definedName>
-    <definedName name="solver_tim" localSheetId="7" hidden="1">2147483647</definedName>
-    <definedName name="solver_tol" localSheetId="7" hidden="1">0.01</definedName>
-    <definedName name="solver_typ" localSheetId="7" hidden="1">2</definedName>
-    <definedName name="solver_val" localSheetId="7" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="7" hidden="1">3</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{D0CA8CA8-9F24-4464-BF8E-62219DCF47F9}"/>
   </extLst>
@@ -126,7 +127,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="139">
   <si>
     <t>n</t>
   </si>
@@ -167,7 +168,7 @@
     <t>l5</t>
   </si>
   <si>
-    <t xml:space="preserve">2 No.</t>
+    <t>2 No.</t>
   </si>
   <si>
     <t>s1</t>
@@ -197,7 +198,7 @@
     <t>zj-cj</t>
   </si>
   <si>
-    <t xml:space="preserve">1 No. Incomplete</t>
+    <t>1 No. Incomplete</t>
   </si>
   <si>
     <t>Z(0,0)</t>
@@ -206,40 +207,40 @@
     <t>Z(0,20)</t>
   </si>
   <si>
-    <t xml:space="preserve">Microsoft Excel 14.0 Answer Report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Worksheet: [405-practical.xlsx]Sheet3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Report Created: 8/30/2026 1:08:34 PM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Result: Solver found a solution.  All Constraints and optimality conditions are satisfied.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solver Engine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Engine: Simplex LP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solution Time: 0.015 Seconds.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iterations: 3 Subproblems: 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Solver Options</t>
+    <t>Microsoft Excel 14.0 Answer Report</t>
+  </si>
+  <si>
+    <t>Worksheet: [405-practical.xlsx]Sheet3</t>
+  </si>
+  <si>
+    <t>Report Created: 8/30/2026 1:08:34 PM</t>
+  </si>
+  <si>
+    <t>Result: Solver found a solution.  All Constraints and optimality conditions are satisfied.</t>
+  </si>
+  <si>
+    <t>Solver Engine</t>
+  </si>
+  <si>
+    <t>Engine: Simplex LP</t>
+  </si>
+  <si>
+    <t>Solution Time: 0.015 Seconds.</t>
+  </si>
+  <si>
+    <t>Iterations: 3 Subproblems: 0</t>
+  </si>
+  <si>
+    <t>Solver Options</t>
   </si>
   <si>
     <t xml:space="preserve">Max Time Unlimited,  Iterations Unlimited, Precision </t>
   </si>
   <si>
-    <t xml:space="preserve">Max Subproblems Unlimited, Max Integer Sols Unlimited, Integer Tolerance %, Assume NonNegative</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Objective Cell (Max)</t>
+    <t>Max Subproblems Unlimited, Max Integer Sols Unlimited, Integer Tolerance %, Assume NonNegative</t>
+  </si>
+  <si>
+    <t>Objective Cell (Max)</t>
   </si>
   <si>
     <t>Cell</t>
@@ -248,16 +249,16 @@
     <t>Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Original Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final Value</t>
+    <t>Original Value</t>
+  </si>
+  <si>
+    <t>Final Value</t>
   </si>
   <si>
     <t>$L$5</t>
   </si>
   <si>
-    <t xml:space="preserve">Variable Cells</t>
+    <t>Variable Cells</t>
   </si>
   <si>
     <t>Integer</t>
@@ -281,7 +282,7 @@
     <t>Constraints</t>
   </si>
   <si>
-    <t xml:space="preserve">Cell Value</t>
+    <t>Cell Value</t>
   </si>
   <si>
     <t>Formula</t>
@@ -314,10 +315,10 @@
     <t>$L$11&lt;=$M$11</t>
   </si>
   <si>
-    <t xml:space="preserve">Not Binding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Excel 14.0 Sensitivity Report</t>
+    <t>Not Binding</t>
+  </si>
+  <si>
+    <t>Microsoft Excel 14.0 Sensitivity Report</t>
   </si>
   <si>
     <t>Final</t>
@@ -359,10 +360,10 @@
     <t>Price</t>
   </si>
   <si>
-    <t xml:space="preserve">R.H. Side</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft Excel 14.0 Limits Report</t>
+    <t>R.H. Side</t>
+  </si>
+  <si>
+    <t>Microsoft Excel 14.0 Limits Report</t>
   </si>
   <si>
     <t>Variable</t>
@@ -380,10 +381,10 @@
     <t>Result</t>
   </si>
   <si>
-    <t xml:space="preserve">2 no. solved by solver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similar type problem of 2</t>
+    <t>2 no. solved by solver</t>
+  </si>
+  <si>
+    <t>Similar type problem of 2</t>
   </si>
   <si>
     <t>Obj</t>
@@ -392,13 +393,13 @@
     <t>&lt;=</t>
   </si>
   <si>
-    <t xml:space="preserve">2 no.</t>
+    <t>2 no.</t>
   </si>
   <si>
     <t>obj</t>
   </si>
   <si>
-    <t xml:space="preserve">3 no.</t>
+    <t>3 no.</t>
   </si>
   <si>
     <t>Source</t>
@@ -516,44 +517,82 @@
   </si>
   <si>
     <t>LL</t>
+  </si>
+  <si>
+    <t>xbar chart</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range </t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>D4</t>
+  </si>
+  <si>
+    <t>UL (xbar)</t>
+  </si>
+  <si>
+    <t>LL (xbar)</t>
+  </si>
+  <si>
+    <t>LL (RC)</t>
+  </si>
+  <si>
+    <t>UL(RC)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11.000000"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color indexed="2"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="18"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11.000000"/>
+      <sz val="11"/>
       <color indexed="2"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -577,31 +616,35 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="16">
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -616,136 +659,136 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="none"/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="none"/>
-      <top style="none"/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="none"/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="23"/>
       </top>
       <bottom style="medium">
         <color indexed="23"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="23"/>
       </top>
       <bottom style="medium">
         <color indexed="23"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="thin">
         <color indexed="23"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
+      <left/>
+      <right/>
       <top style="medium">
         <color indexed="23"/>
       </top>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
-      <left style="none"/>
-      <right style="none"/>
-      <top style="none"/>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
         <color indexed="23"/>
       </bottom>
-      <diagonal style="none"/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -754,73 +797,83 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="none"/>
-      <bottom style="none"/>
-      <diagonal style="none"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+  <cellXfs count="40">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="1" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="3" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="4" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="5" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="6" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="7" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="8" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="2" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="9" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="10" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="11" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="12" numFmtId="0" xfId="0" applyBorder="1"/>
-    <xf fontId="3" fillId="0" borderId="13" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="14" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="0" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="0" fillId="2" borderId="6" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="0" fillId="0" borderId="1" numFmtId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="2" fillId="0" borderId="15" numFmtId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf fontId="0" fillId="4" borderId="1" numFmtId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="0" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFill="1"/>
-    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -836,12 +889,12 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -935,19 +988,18 @@
           <c:smooth val="1"/>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLeaderLines val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
         </c:dLbls>
-        <c:axId val="230986880"/>
-        <c:axId val="230988416"/>
+        <c:axId val="306949504"/>
+        <c:axId val="306955392"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="230986880"/>
+        <c:axId val="306949504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -957,60 +1009,51 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="230988416"/>
+        <c:crossAx val="306955392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="230988416"/>
+        <c:axId val="306955392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr bwMode="auto"/>
-        </c:majorGridlines>
+        <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="230986880"/>
+        <c:crossAx val="306949504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0">
-      <a:off x="5051424" y="914399"/>
-      <a:ext cx="4571999" cy="2698749"/>
-    </a:xfrm>
-  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
-  <c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" r:id="rId1"/>
+  <c:userShapes r:id="rId1"/>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
-  <mc:AlternateContent>
-    <mc:Choice Requires="c14">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
       <c14:style val="102"/>
     </mc:Choice>
     <mc:Fallback>
@@ -1027,6 +1070,17 @@
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$I$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Average</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
@@ -1058,7 +1112,7 @@
                   <c:v>60.8</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>72.6</c:v>
+                  <c:v>72.599999999999994</c:v>
                 </c:pt>
                 <c:pt idx="8">
                   <c:v>62.2</c:v>
@@ -1074,6 +1128,17 @@
         <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$M$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>UL (xbar)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
@@ -1121,6 +1186,17 @@
         <c:ser>
           <c:idx val="2"/>
           <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$N$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LL (xbar)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
@@ -1131,34 +1207,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>43.25440000000001</c:v>
+                  <c:v>43.254400000000011</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1166,21 +1242,20 @@
           <c:smooth val="0"/>
         </c:ser>
         <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLeaderLines val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="231552128"/>
-        <c:axId val="231553664"/>
+        <c:axId val="194644608"/>
+        <c:axId val="195238912"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="231552128"/>
+        <c:axId val="194644608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1189,7 +1264,7 @@
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="231553664"/>
+        <c:crossAx val="195238912"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1197,20 +1272,18 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="231553664"/>
+        <c:axId val="195238912"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr bwMode="auto"/>
-        </c:majorGridlines>
+        <c:majorGridlines/>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="231552128"/>
+        <c:crossAx val="194644608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1224,70 +1297,275 @@
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
-  <c:spPr bwMode="auto">
-    <a:xfrm rot="0">
-      <a:off x="1152524" y="2749549"/>
-      <a:ext cx="4571999" cy="2695574"/>
-    </a:xfrm>
-  </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins l="0.69999999999999996" r="0.69999999999999996" t="0.75" b="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$L$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>R</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$L$3:$L$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>29</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$P$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LL (RC)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$P$3:$P$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet6!$Q$2</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>UL(RC)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet6!$Q$3:$Q$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>69.372</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69.372</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="293600256"/>
+        <c:axId val="306701056"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="293600256"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="306701056"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="306701056"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="293600256"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout/>
+      <c:overlay val="0"/>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
     <c:pageSetup/>
   </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <cdr:relSizeAnchor>
-    <cdr:from>
-      <cdr:x>0.71318999999999999</cdr:x>
-      <cdr:y>0.11458</cdr:y>
-    </cdr:from>
-    <cdr:to>
-      <cdr:x>0.72292000000000001</cdr:x>
-      <cdr:y>0.88541999999999998</cdr:y>
-    </cdr:to>
-    <cdr:cxnSp>
-      <cdr:nvCxnSpPr>
-        <cdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
-        <cdr:cNvCxnSpPr/>
-      </cdr:nvCxnSpPr>
-      <cdr:spPr bwMode="auto">
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="3260725" y="314325"/>
-          <a:ext cx="44450" cy="2114550"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:tailEnd type="arrow"/>
-        </a:ln>
-      </cdr:spPr>
-      <cdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </cdr:style>
-    </cdr:cxnSp>
-  </cdr:relSizeAnchor>
-</c:userShapes>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>174624</xdr:colOff>
@@ -1300,16 +1578,16 @@
       <xdr:row>19</xdr:row>
       <xdr:rowOff>174624</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
         <xdr:cNvPr id="2" name="Chart 1"/>
         <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm rot="0">
-        <a:off x="5051424" y="914399"/>
-        <a:ext cx="4571999" cy="2698749"/>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1319,7 +1597,7 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>488949</xdr:colOff>
@@ -1332,7 +1610,7 @@
       <xdr:row>14</xdr:row>
       <xdr:rowOff>25399</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="4" name="Straight Arrow Connector 3"/>
         <xdr:cNvCxnSpPr/>
@@ -1366,7 +1644,7 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
+  <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>558800</xdr:colOff>
@@ -1379,7 +1657,7 @@
       <xdr:row>18</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp>
+    <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="6" name="Straight Arrow Connector 5"/>
         <xdr:cNvCxnSpPr/>
@@ -1416,31 +1694,76 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:userShapes xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <cdr:relSizeAnchor xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing">
+    <cdr:from>
+      <cdr:x>0.71319</cdr:x>
+      <cdr:y>0.11458</cdr:y>
+    </cdr:from>
+    <cdr:to>
+      <cdr:x>0.72292</cdr:x>
+      <cdr:y>0.88542</cdr:y>
+    </cdr:to>
+    <cdr:cxnSp macro="">
+      <cdr:nvCxnSpPr>
+        <cdr:cNvPr id="3" name="Straight Arrow Connector 2"/>
+        <cdr:cNvCxnSpPr/>
+      </cdr:nvCxnSpPr>
+      <cdr:spPr bwMode="auto">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" flipH="1" flipV="1">
+          <a:off x="3260725" y="314325"/>
+          <a:ext cx="44450" cy="2114550"/>
+        </a:xfrm>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:tailEnd type="arrow"/>
+        </a:ln>
+      </cdr:spPr>
+      <cdr:style>
+        <a:lnRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </cdr:style>
+    </cdr:cxnSp>
+  </cdr:relSizeAnchor>
+</c:userShapes>
+</file>
+
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
-  <xdr:twoCellAnchor editAs="twoCell">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>542924</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>34924</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>238124</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>15874</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="8" name="Chart 7"/>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-        </xdr:cNvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4"/>
+        <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
-      <xdr:xfrm rot="0">
-        <a:off x="1152524" y="2749549"/>
-        <a:ext cx="4571999" cy="2695574"/>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1450,294 +1773,41 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1953,19 +2023,21 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
         <v>1</v>
       </c>
@@ -1973,7 +2045,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -1990,7 +2062,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C5">
         <v>3</v>
       </c>
@@ -2001,7 +2073,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D6">
         <v>5</v>
       </c>
@@ -2012,7 +2084,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>5</v>
       </c>
@@ -2023,7 +2095,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C9">
         <v>9</v>
       </c>
@@ -2031,7 +2103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>6</v>
       </c>
@@ -2039,12 +2111,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C13">
         <v>0</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
         <v>7</v>
       </c>
@@ -2052,12 +2124,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C17">
         <v>4</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
         <v>8</v>
       </c>
@@ -2068,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C20">
         <v>0</v>
       </c>
@@ -2076,7 +2148,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>9</v>
       </c>
@@ -2087,7 +2159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C23">
         <v>0</v>
       </c>
@@ -2095,7 +2167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
         <v>10</v>
       </c>
@@ -2106,7 +2178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C26">
         <v>0</v>
       </c>
@@ -2114,7 +2186,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
         <v>11</v>
       </c>
@@ -2125,7 +2197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C30">
         <v>0</v>
       </c>
@@ -2133,7 +2205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>12</v>
       </c>
@@ -2144,7 +2216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
       <c r="C34">
         <v>0</v>
       </c>
@@ -2153,24 +2225,23 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="C2:L34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D3" s="1"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
@@ -2188,7 +2259,7 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
     </row>
-    <row r="4">
+    <row r="4" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D4" s="1"/>
       <c r="E4" s="2" t="s">
         <v>16</v>
@@ -2212,7 +2283,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D5" s="1">
         <v>0</v>
       </c>
@@ -2239,7 +2310,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D6" s="1">
         <v>0</v>
       </c>
@@ -2266,7 +2337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D7" s="1"/>
       <c r="E7" s="2" t="s">
         <v>21</v>
@@ -2293,7 +2364,7 @@
       </c>
       <c r="K7" s="2"/>
     </row>
-    <row r="8">
+    <row r="8" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D8" s="1"/>
       <c r="E8" s="2" t="s">
         <v>22</v>
@@ -2317,7 +2388,7 @@
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9">
+    <row r="9" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
@@ -2326,7 +2397,7 @@
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
     </row>
-    <row r="10">
+    <row r="10" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D10" s="1">
         <v>0</v>
       </c>
@@ -2358,7 +2429,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D11" s="1">
         <v>40</v>
       </c>
@@ -2390,7 +2461,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D12" s="1"/>
       <c r="E12" s="2" t="s">
         <v>21</v>
@@ -2417,7 +2488,7 @@
       </c>
       <c r="K12" s="2"/>
     </row>
-    <row r="13">
+    <row r="13" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D13" s="1"/>
       <c r="E13" s="2" t="s">
         <v>22</v>
@@ -2441,7 +2512,7 @@
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14">
+    <row r="14" spans="4:11" x14ac:dyDescent="0.25">
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
@@ -2450,7 +2521,7 @@
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
     </row>
-    <row r="15">
+    <row r="15" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D15" s="1">
         <v>15</v>
       </c>
@@ -2467,11 +2538,11 @@
       </c>
       <c r="H15" s="2">
         <f t="shared" si="5"/>
-        <v>0.80000000000000004</v>
+        <v>0.8</v>
       </c>
       <c r="I15" s="2">
         <f t="shared" si="5"/>
-        <v>-0.59999999999999998</v>
+        <v>-0.6</v>
       </c>
       <c r="J15" s="2">
         <f t="shared" si="5"/>
@@ -2479,7 +2550,7 @@
       </c>
       <c r="K15" s="4"/>
     </row>
-    <row r="16">
+    <row r="16" spans="4:11" x14ac:dyDescent="0.25">
       <c r="D16" s="1">
         <v>40</v>
       </c>
@@ -2496,11 +2567,11 @@
       </c>
       <c r="H16" s="2">
         <f t="shared" si="6"/>
-        <v>-0.20000000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="I16" s="2">
         <f t="shared" si="6"/>
-        <v>0.40000000000000002</v>
+        <v>0.4</v>
       </c>
       <c r="J16" s="2">
         <f t="shared" si="6"/>
@@ -2508,7 +2579,7 @@
       </c>
       <c r="K16" s="4"/>
     </row>
-    <row r="17">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D17" s="1"/>
       <c r="E17" s="2" t="s">
         <v>21</v>
@@ -2535,7 +2606,7 @@
       </c>
       <c r="K17" s="4"/>
     </row>
-    <row r="18">
+    <row r="18" spans="3:12" x14ac:dyDescent="0.25">
       <c r="D18" s="1"/>
       <c r="E18" s="2" t="s">
         <v>22</v>
@@ -2559,7 +2630,7 @@
       <c r="J18" s="2"/>
       <c r="K18" s="4"/>
     </row>
-    <row r="19">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="4"/>
@@ -2568,7 +2639,7 @@
       <c r="J19" s="4"/>
       <c r="K19" s="4"/>
     </row>
-    <row r="20">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="4"/>
@@ -2577,7 +2648,7 @@
       <c r="J20" s="4"/>
       <c r="K20" s="4"/>
     </row>
-    <row r="21">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
@@ -2586,7 +2657,7 @@
       <c r="J21" s="4"/>
       <c r="K21" s="4"/>
     </row>
-    <row r="22">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="4"/>
@@ -2595,572 +2666,570 @@
       <c r="J22" s="4"/>
       <c r="K22" s="4"/>
     </row>
-    <row r="23">
-      <c r="C23" s="5" t="s">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C23" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="5"/>
-    </row>
-    <row r="24">
-      <c r="C24" s="6"/>
-      <c r="D24" s="7" t="s">
+      <c r="D23" s="34"/>
+    </row>
+    <row r="24" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C24" s="5"/>
+      <c r="D24" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E24" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7" t="s">
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="L24" s="8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="C25" s="9" t="s">
+      <c r="L24" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C25" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D25" s="10">
-        <v>0</v>
-      </c>
-      <c r="E25" s="10">
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
         <f>G25/3</f>
         <v>20</v>
       </c>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10">
+      <c r="F25" s="9"/>
+      <c r="G25" s="9">
         <v>60</v>
       </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-      <c r="K25" s="10" t="s">
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="10">
         <f>135*20</f>
         <v>2700</v>
       </c>
     </row>
-    <row r="26">
-      <c r="C26" s="9"/>
-      <c r="D26" s="10">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C26" s="8"/>
+      <c r="D26" s="9">
         <v>30</v>
       </c>
-      <c r="E26" s="10">
-        <v>0</v>
-      </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="11">
+      <c r="E26" s="9">
+        <v>0</v>
+      </c>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="10">
         <f>18*140+135*8</f>
         <v>3600</v>
       </c>
     </row>
-    <row r="27">
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-      <c r="K27" s="10"/>
-      <c r="L27" s="11"/>
-    </row>
-    <row r="28">
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-      <c r="K28" s="10"/>
-      <c r="L28" s="11"/>
-    </row>
-    <row r="29">
-      <c r="C29" s="9" t="s">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C27" s="8"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="10"/>
+    </row>
+    <row r="28" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C28" s="8"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="10"/>
+    </row>
+    <row r="29" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C29" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="D29" s="10">
-        <v>0</v>
-      </c>
-      <c r="E29" s="10">
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
         <f>G29/3</f>
         <v>32</v>
       </c>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10">
+      <c r="F29" s="9"/>
+      <c r="G29" s="9">
         <v>96</v>
       </c>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-      <c r="K29" s="10"/>
-      <c r="L29" s="11"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="9"/>
-      <c r="D30" s="10">
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="10"/>
+    </row>
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C30" s="8"/>
+      <c r="D30" s="9">
         <f>96/4</f>
         <v>24</v>
       </c>
-      <c r="E30" s="10">
-        <v>0</v>
-      </c>
-      <c r="F30" s="10"/>
-      <c r="G30" s="10"/>
-      <c r="H30" s="10"/>
-      <c r="I30" s="10"/>
-      <c r="J30" s="10"/>
-      <c r="K30" s="10"/>
-      <c r="L30" s="11"/>
-    </row>
-    <row r="31">
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-      <c r="F31" s="10"/>
-      <c r="G31" s="10"/>
-      <c r="H31" s="10"/>
-      <c r="I31" s="10"/>
-      <c r="J31" s="10"/>
-      <c r="K31" s="10"/>
-      <c r="L31" s="11"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="10"/>
-      <c r="F32" s="10"/>
-      <c r="G32" s="10"/>
-      <c r="H32" s="10"/>
-      <c r="I32" s="10"/>
-      <c r="J32" s="10"/>
-      <c r="K32" s="10"/>
-      <c r="L32" s="11"/>
-    </row>
-    <row r="33">
-      <c r="C33" s="9" t="s">
+      <c r="E30" s="9">
+        <v>0</v>
+      </c>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="10"/>
+    </row>
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C31" s="8"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="10"/>
+    </row>
+    <row r="32" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C32" s="8"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="10"/>
+    </row>
+    <row r="33" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C33" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D33" s="10">
-        <v>0</v>
-      </c>
-      <c r="E33" s="10">
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
         <f>105/3.5</f>
         <v>30</v>
       </c>
-      <c r="F33" s="10"/>
-      <c r="G33" s="10">
+      <c r="F33" s="9"/>
+      <c r="G33" s="9">
         <v>105</v>
       </c>
-      <c r="H33" s="10"/>
-      <c r="I33" s="10"/>
-      <c r="J33" s="10"/>
-      <c r="K33" s="10"/>
-      <c r="L33" s="11"/>
-    </row>
-    <row r="34">
-      <c r="C34" s="12"/>
-      <c r="D34" s="13">
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="3:12" x14ac:dyDescent="0.25">
+      <c r="C34" s="11"/>
+      <c r="D34" s="12">
         <f>105/4</f>
         <v>26.25</v>
       </c>
-      <c r="E34" s="13">
-        <v>0</v>
-      </c>
-      <c r="F34" s="13"/>
-      <c r="G34" s="13"/>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
-      <c r="K34" s="13"/>
-      <c r="L34" s="14"/>
+      <c r="E34" s="12">
+        <v>0</v>
+      </c>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="C23:D23"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.1796875"/>
-    <col customWidth="1" min="2" max="2" width="5.6328125"/>
-    <col customWidth="1" min="3" max="3" width="5.7265625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="12.453125"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="13.453125"/>
-    <col customWidth="1" min="6" max="6" width="10.453125"/>
-    <col customWidth="1" min="7" max="7" width="5"/>
+    <col min="1" max="1" width="2.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="15" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="15"/>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14"/>
       <c r="B6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="15"/>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
       <c r="B7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="15"/>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="14"/>
       <c r="B8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="14" ht="15">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15" ht="15">
-      <c r="B15" s="16" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="15" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" ht="15">
-      <c r="B16" s="17" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17">
+      <c r="C16" s="16"/>
+      <c r="D16" s="16">
         <v>16440</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E16" s="16">
         <v>16440</v>
       </c>
     </row>
-    <row r="19" ht="15">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="20" ht="15">
-      <c r="B20" s="16" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="18" t="s">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="17">
         <v>80</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="17">
         <v>80</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="18" t="s">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="18">
+      <c r="D22" s="17">
         <v>120</v>
       </c>
-      <c r="E22" s="18">
+      <c r="E22" s="17">
         <v>120</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="F22" s="17" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="23" ht="15">
-      <c r="B23" s="17" t="s">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="C23" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="17">
-        <v>0</v>
-      </c>
-      <c r="E23" s="17">
-        <v>0</v>
-      </c>
-      <c r="F23" s="17" t="s">
+      <c r="D23" s="16">
+        <v>0</v>
+      </c>
+      <c r="E23" s="16">
+        <v>0</v>
+      </c>
+      <c r="F23" s="16" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="26" ht="15">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="27" ht="15">
-      <c r="B27" s="16" t="s">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="G27" s="16" t="s">
+      <c r="G27" s="15" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="18" t="s">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C28" s="18"/>
-      <c r="D28" s="18">
+      <c r="C28" s="17"/>
+      <c r="D28" s="17">
         <v>200</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G28" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="18" t="s">
+      <c r="G28" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18">
+      <c r="C29" s="17"/>
+      <c r="D29" s="17">
         <v>320</v>
       </c>
-      <c r="E29" s="18" t="s">
+      <c r="E29" s="17" t="s">
         <v>59</v>
       </c>
-      <c r="F29" s="18" t="s">
+      <c r="F29" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G29" s="18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="15">
-      <c r="B30" s="17" t="s">
+      <c r="G29" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B30" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16">
         <v>2080</v>
       </c>
-      <c r="E30" s="17" t="s">
+      <c r="E30" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="F30" s="17" t="s">
+      <c r="F30" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="16">
         <v>320</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.1796875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="5.6328125"/>
-    <col customWidth="1" min="3" max="3" width="5.7265625"/>
-    <col customWidth="1" min="4" max="4" width="5.54296875"/>
-    <col bestFit="1" customWidth="1" min="5" max="5" width="8"/>
-    <col bestFit="1" customWidth="1" min="6" max="6" width="9.81640625"/>
-    <col bestFit="1" customWidth="1" min="7" max="8" width="9"/>
+    <col min="1" max="1" width="2.140625" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.7109375" customWidth="1"/>
+    <col min="4" max="4" width="5.5703125" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="6" ht="15">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" ht="15">
-      <c r="B8" s="20" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H8" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="I8" s="21" t="s">
+      <c r="I8" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="18" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <v>80</v>
       </c>
-      <c r="E9" s="18">
-        <v>0</v>
-      </c>
-      <c r="F9" s="18">
+      <c r="E9" s="17">
+        <v>0</v>
+      </c>
+      <c r="F9" s="17">
         <v>63</v>
       </c>
-      <c r="G9" s="18">
+      <c r="G9" s="17">
         <v>32</v>
       </c>
-      <c r="H9" s="18">
+      <c r="H9" s="17">
         <v>15.5</v>
       </c>
       <c r="I9">
@@ -3172,424 +3241,420 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="18" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <v>120</v>
       </c>
-      <c r="E10" s="18">
-        <v>0</v>
-      </c>
-      <c r="F10" s="18">
+      <c r="E10" s="17">
+        <v>0</v>
+      </c>
+      <c r="F10" s="17">
         <v>95</v>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <v>31</v>
       </c>
-      <c r="H10" s="18">
+      <c r="H10" s="17">
         <v>27.5</v>
       </c>
       <c r="I10">
-        <f t="shared" ref="I10:I11" si="7">F10+G10</f>
+        <f t="shared" ref="I10:I11" si="0">F10+G10</f>
         <v>126</v>
       </c>
       <c r="J10">
-        <f t="shared" ref="J10:J11" si="8">F10-H10</f>
+        <f t="shared" ref="J10:J11" si="1">F10-H10</f>
         <v>67.5</v>
       </c>
     </row>
-    <row r="11" ht="15">
-      <c r="B11" s="17" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D11" s="17">
-        <v>0</v>
-      </c>
-      <c r="E11" s="17">
+      <c r="D11" s="16">
+        <v>0</v>
+      </c>
+      <c r="E11" s="16">
         <v>-55</v>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="16">
         <v>135</v>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="16">
         <v>55</v>
       </c>
-      <c r="H11" s="17">
-        <v>1e+30</v>
+      <c r="H11" s="16">
+        <v>1E+30</v>
       </c>
       <c r="I11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="0"/>
         <v>190</v>
       </c>
       <c r="J11">
-        <f t="shared" si="8"/>
-        <v>-1e+30</v>
-      </c>
-    </row>
-    <row r="13" ht="15">
+        <f t="shared" si="1"/>
+        <v>-1E+30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="19"/>
-      <c r="C14" s="19"/>
-      <c r="D14" s="19" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="19" t="s">
+      <c r="G14" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H14" s="19" t="s">
+      <c r="H14" s="18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" ht="15">
-      <c r="B15" s="20" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="H15" s="20" t="s">
+      <c r="H15" s="19" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="18" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18">
+      <c r="C16" s="17"/>
+      <c r="D16" s="17">
         <v>200</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="17">
         <v>31</v>
       </c>
-      <c r="F16" s="18">
+      <c r="F16" s="17">
         <v>200</v>
       </c>
-      <c r="G16" s="18">
+      <c r="G16" s="17">
         <v>80</v>
       </c>
-      <c r="H16" s="18">
+      <c r="H16" s="17">
         <v>40</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="18" t="s">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18">
+      <c r="C17" s="17"/>
+      <c r="D17" s="17">
         <v>320</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="17">
         <v>32</v>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="17">
         <v>320</v>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="17">
         <v>80</v>
       </c>
-      <c r="H17" s="18">
+      <c r="H17" s="17">
         <v>120</v>
       </c>
     </row>
-    <row r="18" ht="15">
-      <c r="B18" s="17" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17">
+      <c r="C18" s="16"/>
+      <c r="D18" s="16">
         <v>2080</v>
       </c>
-      <c r="E18" s="17">
-        <v>0</v>
-      </c>
-      <c r="F18" s="17">
+      <c r="E18" s="16">
+        <v>0</v>
+      </c>
+      <c r="F18" s="16">
         <v>2400</v>
       </c>
-      <c r="G18" s="17">
-        <v>1e+30</v>
-      </c>
-      <c r="H18" s="17">
+      <c r="G18" s="16">
+        <v>1E+30</v>
+      </c>
+      <c r="H18" s="16">
         <v>320</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.1796875"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="4.81640625"/>
-    <col bestFit="1" customWidth="1" min="3" max="3" width="8.7265625"/>
-    <col bestFit="1" customWidth="1" min="4" max="4" width="5.81640625"/>
-    <col customWidth="1" min="5" max="5" width="2.1796875"/>
-    <col customWidth="1" min="6" max="6" width="5.90625"/>
-    <col customWidth="1" min="8" max="8" width="2.1796875"/>
-    <col customWidth="1" min="9" max="9" width="6"/>
+    <col min="1" max="1" width="2.140625" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2.140625" customWidth="1"/>
+    <col min="6" max="6" width="5.85546875" customWidth="1"/>
+    <col min="8" max="8" width="2.140625" customWidth="1"/>
+    <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="15" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" ht="15"/>
-    <row r="6">
-      <c r="B6" s="19"/>
-      <c r="C6" s="19" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="19"/>
-    </row>
-    <row r="7" ht="15">
-      <c r="B7" s="20" t="s">
+      <c r="D6" s="18"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="8" ht="15">
-      <c r="B8" s="17" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16">
         <v>16440</v>
       </c>
     </row>
-    <row r="10" ht="15"/>
-    <row r="11">
-      <c r="B11" s="19"/>
-      <c r="C11" s="19" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="D11" s="19"/>
-      <c r="F11" s="19" t="s">
+      <c r="D11" s="18"/>
+      <c r="F11" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="G11" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="19" t="s">
+      <c r="I11" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="J11" s="19" t="s">
+      <c r="J11" s="18" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" ht="15">
-      <c r="B12" s="20" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="G12" s="20" t="s">
+      <c r="G12" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="I12" s="20" t="s">
+      <c r="I12" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="J12" s="20" t="s">
+      <c r="J12" s="19" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="18" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <v>80</v>
       </c>
-      <c r="F13" s="18">
-        <v>0</v>
-      </c>
-      <c r="G13" s="18">
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
         <v>11400</v>
       </c>
-      <c r="I13" s="18">
+      <c r="I13" s="17">
         <v>80</v>
       </c>
-      <c r="J13" s="18">
+      <c r="J13" s="17">
         <v>16440</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="18" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <v>120</v>
       </c>
-      <c r="F14" s="18">
-        <v>0</v>
-      </c>
-      <c r="G14" s="18">
+      <c r="F14" s="17">
+        <v>0</v>
+      </c>
+      <c r="G14" s="17">
         <v>5040</v>
       </c>
-      <c r="I14" s="18">
+      <c r="I14" s="17">
         <v>120</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="17">
         <v>16440</v>
       </c>
     </row>
-    <row r="15" ht="15">
-      <c r="B15" s="17" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="C15" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
+      <c r="D15" s="16">
+        <v>0</v>
+      </c>
+      <c r="F15" s="16">
+        <v>0</v>
+      </c>
+      <c r="G15" s="16">
         <v>16440</v>
       </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
+      <c r="I15" s="16">
+        <v>0</v>
+      </c>
+      <c r="J15" s="16">
         <v>16440</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="5.08984375"/>
+    <col min="5" max="5" width="5.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="H1" s="5" t="s">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="H1" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="6"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="8"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="10" t="s">
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="H2" s="5"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="7"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="8"/>
+      <c r="B3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="10" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="L3" s="10"/>
-      <c r="M3" s="10"/>
-      <c r="N3" s="11"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="9" t="s">
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="10"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="4">
@@ -3598,350 +3663,349 @@
       <c r="C4" s="4">
         <v>40</v>
       </c>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
-      <c r="H4" s="9" t="s">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10"/>
+      <c r="H4" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="9">
         <v>63</v>
       </c>
-      <c r="J4" s="10">
+      <c r="J4" s="9">
         <v>95</v>
       </c>
-      <c r="K4" s="10">
+      <c r="K4" s="9">
         <v>135</v>
       </c>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
-      <c r="N4" s="11"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="9"/>
-      <c r="B5" s="22">
+      <c r="L4" s="9"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="B5" s="21">
         <v>24</v>
       </c>
-      <c r="C5" s="22">
+      <c r="C5" s="21">
         <v>4</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="22">
         <f>SUMPRODUCT(B4:C4,B5:C5)</f>
         <v>520</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="22">
+      <c r="E5" s="9"/>
+      <c r="F5" s="10"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="21">
         <v>80</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="21">
         <v>120</v>
       </c>
-      <c r="K5" s="22">
-        <v>0</v>
-      </c>
-      <c r="L5" s="10">
+      <c r="K5" s="21">
+        <v>0</v>
+      </c>
+      <c r="L5" s="9">
         <f>SUMPRODUCT(I4:K4,I5:K5)</f>
         <v>16440</v>
       </c>
-      <c r="M5" s="10"/>
-      <c r="N5" s="11"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="9"/>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="11"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="s">
+      <c r="M5" s="9"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="10"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="9"/>
+      <c r="J6" s="9"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <f>Sheet2!F5</f>
         <v>2</v>
       </c>
-      <c r="C7" s="10">
+      <c r="C7" s="9">
         <f>Sheet2!G5</f>
         <v>3</v>
       </c>
-      <c r="D7" s="22">
-        <f t="shared" ref="D7:D8" si="9">SUMPRODUCT(B$5:C$5,B7:C7)</f>
+      <c r="D7" s="21">
+        <f t="shared" ref="D7:D8" si="0">SUMPRODUCT(B$5:C$5,B7:C7)</f>
         <v>60</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <v>60</v>
       </c>
-      <c r="H7" s="9"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="11"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="s">
+      <c r="H7" s="8"/>
+      <c r="I7" s="21"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="21"/>
+      <c r="L7" s="9"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="10"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <f>Sheet2!F6</f>
         <v>1</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="9">
         <f>Sheet2!G6</f>
         <v>4</v>
       </c>
-      <c r="D8" s="22">
-        <f t="shared" si="9"/>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <v>40</v>
       </c>
-      <c r="H8" s="9"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="9"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="11"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="10">
+      <c r="H8" s="8"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="9"/>
+      <c r="K8" s="9"/>
+      <c r="L8" s="9"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="10"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="10"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="9">
         <v>1</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J9" s="9">
         <v>1</v>
       </c>
-      <c r="K9" s="10">
+      <c r="K9" s="9">
         <v>2</v>
       </c>
-      <c r="L9" s="10">
+      <c r="L9" s="9">
         <f>SUMPRODUCT(I$5:K$5,I9:K9)</f>
         <v>200</v>
       </c>
-      <c r="M9" s="10">
+      <c r="M9" s="9">
         <v>200</v>
       </c>
-      <c r="N9" s="11"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="9"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="11"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10">
+      <c r="N9" s="10"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="9">
         <v>1</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J10" s="9">
         <v>2</v>
       </c>
-      <c r="K10" s="10">
+      <c r="K10" s="9">
         <v>4</v>
       </c>
-      <c r="L10" s="10">
-        <f t="shared" ref="L10:L11" si="10">SUMPRODUCT(I$5:K$5,I10:K10)</f>
+      <c r="L10" s="9">
+        <f t="shared" ref="L10:L11" si="1">SUMPRODUCT(I$5:K$5,I10:K10)</f>
         <v>320</v>
       </c>
-      <c r="M10" s="10">
+      <c r="M10" s="9">
         <v>320</v>
       </c>
-      <c r="N10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10">
+      <c r="N10" s="10"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="13"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="9">
         <v>8</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J11" s="9">
         <v>12</v>
       </c>
-      <c r="K11" s="10">
+      <c r="K11" s="9">
         <v>14</v>
       </c>
-      <c r="L11" s="10">
-        <f t="shared" si="10"/>
+      <c r="L11" s="9">
+        <f t="shared" si="1"/>
         <v>2080</v>
       </c>
-      <c r="M11" s="10">
+      <c r="M11" s="9">
         <v>2400</v>
       </c>
-      <c r="N11" s="11"/>
-    </row>
-    <row r="12">
-      <c r="H12" s="12"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="14"/>
-    </row>
-    <row r="14">
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H12" s="11"/>
+      <c r="I12" s="12"/>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="12"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="13"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="6" t="s">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="B15" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="8"/>
-    </row>
-    <row r="16">
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>15</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="9">
         <v>40</v>
       </c>
-      <c r="D16" s="10"/>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="11"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="25">
-        <v>0</v>
-      </c>
-      <c r="C17" s="22">
-        <v>0</v>
-      </c>
-      <c r="D17" s="10">
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="10"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="24">
+        <v>0</v>
+      </c>
+      <c r="C17" s="21">
+        <v>0</v>
+      </c>
+      <c r="D17" s="9">
         <f>SUMPRODUCT(B16:C16,B17:C17)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="11"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="9"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="11"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="9"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="11"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="9"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="11"/>
-    </row>
-    <row r="21">
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="10"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="8"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="10"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="8"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="10"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="8"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="10"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="9">
+      <c r="B21" s="8">
         <v>2</v>
       </c>
-      <c r="C21" s="10">
+      <c r="C21" s="9">
         <v>3</v>
       </c>
-      <c r="D21" s="10">
-        <f t="shared" ref="D21:D22" si="11">SUMPRODUCT(B$17:C$17,B21:C21)</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="D21" s="9">
+        <f t="shared" ref="D21:D22" si="2">SUMPRODUCT(B$17:C$17,B21:C21)</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F21" s="9">
         <v>60</v>
       </c>
-      <c r="G21" s="11"/>
-    </row>
-    <row r="22">
+      <c r="G21" s="10"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="12">
+      <c r="B22" s="11">
         <v>1</v>
       </c>
-      <c r="C22" s="13">
+      <c r="C22" s="12">
         <v>4</v>
       </c>
-      <c r="D22" s="13">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="E22" s="13" t="s">
+      <c r="D22" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E22" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="12">
         <v>40</v>
       </c>
-      <c r="G22" s="14"/>
+      <c r="G22" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="H1:J1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:G20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>90</v>
       </c>
@@ -3950,23 +4014,23 @@
         <v>150</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="4"/>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="G3" s="36" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4"/>
-      <c r="B4" s="26"/>
+      <c r="B4" s="35"/>
       <c r="C4" s="2" t="s">
         <v>94</v>
       </c>
@@ -3976,75 +4040,75 @@
       <c r="E4" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5">
+      <c r="G4" s="36"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4"/>
       <c r="B5" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="27">
-        <v>0</v>
-      </c>
-      <c r="D5" s="27">
+      <c r="C5" s="25">
+        <v>0</v>
+      </c>
+      <c r="D5" s="25">
         <v>15</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="25">
         <v>35</v>
       </c>
-      <c r="F5" s="15">
-        <f t="shared" ref="F5:F7" si="12">SUM(C5:E5)</f>
+      <c r="F5" s="14">
+        <f t="shared" ref="F5:F7" si="0">SUM(C5:E5)</f>
         <v>50</v>
       </c>
       <c r="G5" s="2">
         <v>50</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4"/>
       <c r="B6" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="27">
-        <v>0</v>
-      </c>
-      <c r="D6" s="27">
+      <c r="C6" s="25">
+        <v>0</v>
+      </c>
+      <c r="D6" s="25">
         <v>40</v>
       </c>
-      <c r="E6" s="27">
-        <v>0</v>
-      </c>
-      <c r="F6" s="15">
-        <f t="shared" si="12"/>
+      <c r="E6" s="25">
+        <v>0</v>
+      </c>
+      <c r="F6" s="14">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="G6" s="2">
         <v>40</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
       <c r="B7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="25">
         <v>20</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="25">
         <v>40</v>
       </c>
-      <c r="E7" s="27">
-        <v>0</v>
-      </c>
-      <c r="F7" s="15">
-        <f t="shared" si="12"/>
+      <c r="E7" s="25">
+        <v>0</v>
+      </c>
+      <c r="F7" s="14">
+        <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="G7" s="2">
         <v>60</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <f>SUM(C9:E9)</f>
         <v>150</v>
@@ -4052,23 +4116,23 @@
       <c r="B8" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="14">
         <f>SUM(C5:C7)</f>
         <v>20</v>
       </c>
-      <c r="D8" s="15">
-        <f t="shared" ref="D8:E8" si="13">SUM(D5:D7)</f>
+      <c r="D8" s="14">
+        <f t="shared" ref="D8:E8" si="1">SUM(D5:D7)</f>
         <v>95</v>
       </c>
-      <c r="E8" s="15">
-        <f t="shared" si="13"/>
+      <c r="E8" s="14">
+        <f t="shared" si="1"/>
         <v>35</v>
       </c>
       <c r="G8" s="2">
         <v>150</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
         <v>101</v>
       </c>
@@ -4082,30 +4146,30 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>102</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="26">
         <f>SUMPRODUCT(C5:E7,C17:E19)</f>
         <v>920</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="26" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="35" t="s">
         <v>91</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2" t="s">
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="26"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="35"/>
       <c r="C16" s="2" t="s">
         <v>94</v>
       </c>
@@ -4115,9 +4179,9 @@
       <c r="E16" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17">
+      <c r="F16" s="36"/>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="2" t="s">
         <v>97</v>
       </c>
@@ -4134,7 +4198,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
         <v>98</v>
       </c>
@@ -4151,7 +4215,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="2" t="s">
         <v>99</v>
       </c>
@@ -4168,7 +4232,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
         <v>101</v>
       </c>
@@ -4194,63 +4258,62 @@
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="F15:F16"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:P40"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1">
         <f>SUM(I4:I9)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="2">
-      <c r="B2" s="29" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29" t="s">
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="38" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" s="29"/>
-      <c r="C3" s="30" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="38"/>
+      <c r="C3" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="D3" s="30" t="s">
+      <c r="D3" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="30" t="s">
+      <c r="E3" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F3" s="30" t="s">
+      <c r="F3" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="G3" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="H3" s="30" t="s">
+      <c r="H3" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="I3" s="29"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="30" t="s">
+      <c r="I3" s="38"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="28" t="s">
         <v>112</v>
       </c>
       <c r="C4" s="1">
@@ -4275,8 +4338,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="30" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="28" t="s">
         <v>113</v>
       </c>
       <c r="C5" s="1">
@@ -4301,8 +4364,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="30" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="28" t="s">
         <v>114</v>
       </c>
       <c r="C6" s="1">
@@ -4327,8 +4390,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="30" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="28" t="s">
         <v>115</v>
       </c>
       <c r="C7" s="1">
@@ -4353,8 +4416,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="30" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="s">
         <v>116</v>
       </c>
       <c r="C8" s="1">
@@ -4379,8 +4442,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="30" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
         <v>117</v>
       </c>
       <c r="C9" s="1">
@@ -4405,12 +4468,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>SUM(C10:H10)</f>
         <v>100</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="28" t="s">
         <v>101</v>
       </c>
       <c r="C10" s="1">
@@ -4433,259 +4496,259 @@
       </c>
       <c r="I10" s="1"/>
     </row>
-    <row r="12">
-      <c r="B12" s="29" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="38" t="s">
         <v>103</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="38" t="s">
         <v>104</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="J12" s="29" t="s">
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="27"/>
+      <c r="J12" s="38" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="29"/>
-      <c r="C13" s="30" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="38"/>
+      <c r="C13" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D13" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="30" t="s">
+      <c r="E13" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="30" t="s">
+      <c r="F13" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="30" t="s">
+      <c r="H13" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="31" t="s">
+      <c r="I13" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="J13" s="29"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="30" t="s">
+      <c r="J13" s="38"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="30">
         <v>10</v>
       </c>
-      <c r="D14" s="32">
-        <v>0</v>
-      </c>
-      <c r="E14" s="32">
-        <v>0</v>
-      </c>
-      <c r="F14" s="32">
-        <v>0</v>
-      </c>
-      <c r="G14" s="32">
+      <c r="D14" s="30">
+        <v>0</v>
+      </c>
+      <c r="E14" s="30">
+        <v>0</v>
+      </c>
+      <c r="F14" s="30">
+        <v>0</v>
+      </c>
+      <c r="G14" s="30">
         <v>5</v>
       </c>
-      <c r="H14" s="32">
-        <v>0</v>
-      </c>
-      <c r="I14" s="33">
-        <f t="shared" ref="I14:I19" si="14">SUM(C14:H14)</f>
+      <c r="H14" s="30">
+        <v>0</v>
+      </c>
+      <c r="I14" s="31">
+        <f t="shared" ref="I14:I19" si="0">SUM(C14:H14)</f>
         <v>15</v>
       </c>
       <c r="J14" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="30" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="C15" s="32">
-        <v>0</v>
-      </c>
-      <c r="D15" s="32">
-        <v>0</v>
-      </c>
-      <c r="E15" s="32">
-        <v>0</v>
-      </c>
-      <c r="F15" s="32">
-        <v>0</v>
-      </c>
-      <c r="G15" s="32">
+      <c r="C15" s="30">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30">
+        <v>0</v>
+      </c>
+      <c r="E15" s="30">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30">
         <v>10</v>
       </c>
-      <c r="H15" s="32">
-        <v>0</v>
-      </c>
-      <c r="I15" s="33">
-        <f t="shared" si="14"/>
+      <c r="H15" s="30">
+        <v>0</v>
+      </c>
+      <c r="I15" s="31">
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="J15" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="30" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="C16" s="32">
-        <v>0</v>
-      </c>
-      <c r="D16" s="32">
-        <v>0</v>
-      </c>
-      <c r="E16" s="32">
-        <v>0</v>
-      </c>
-      <c r="F16" s="32">
-        <v>0</v>
-      </c>
-      <c r="G16" s="32">
+      <c r="C16" s="30">
+        <v>0</v>
+      </c>
+      <c r="D16" s="30">
+        <v>0</v>
+      </c>
+      <c r="E16" s="30">
+        <v>0</v>
+      </c>
+      <c r="F16" s="30">
+        <v>0</v>
+      </c>
+      <c r="G16" s="30">
         <v>15</v>
       </c>
-      <c r="H16" s="32">
-        <v>0</v>
-      </c>
-      <c r="I16" s="33">
-        <f t="shared" si="14"/>
+      <c r="H16" s="30">
+        <v>0</v>
+      </c>
+      <c r="I16" s="31">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="J16" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="30" t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B17" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="C17" s="32">
-        <v>0</v>
-      </c>
-      <c r="D17" s="32">
-        <v>0</v>
-      </c>
-      <c r="E17" s="32">
-        <v>0</v>
-      </c>
-      <c r="F17" s="32">
+      <c r="C17" s="30">
+        <v>0</v>
+      </c>
+      <c r="D17" s="30">
+        <v>0</v>
+      </c>
+      <c r="E17" s="30">
+        <v>0</v>
+      </c>
+      <c r="F17" s="30">
         <v>15</v>
       </c>
-      <c r="G17" s="32">
-        <v>0</v>
-      </c>
-      <c r="H17" s="32">
+      <c r="G17" s="30">
+        <v>0</v>
+      </c>
+      <c r="H17" s="30">
         <v>10</v>
       </c>
-      <c r="I17" s="33">
-        <f t="shared" si="14"/>
+      <c r="I17" s="31">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="J17" s="1">
         <v>25</v>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" s="30" t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B18" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="C18" s="32">
-        <v>0</v>
-      </c>
-      <c r="D18" s="32">
-        <v>0</v>
-      </c>
-      <c r="E18" s="32">
+      <c r="C18" s="30">
+        <v>0</v>
+      </c>
+      <c r="D18" s="30">
+        <v>0</v>
+      </c>
+      <c r="E18" s="30">
         <v>5</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="30">
         <v>10</v>
       </c>
-      <c r="G18" s="32">
-        <v>0</v>
-      </c>
-      <c r="H18" s="32">
-        <v>0</v>
-      </c>
-      <c r="I18" s="33">
-        <f t="shared" si="14"/>
+      <c r="G18" s="30">
+        <v>0</v>
+      </c>
+      <c r="H18" s="30">
+        <v>0</v>
+      </c>
+      <c r="I18" s="31">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="J18" s="1">
         <v>15</v>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="30" t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="32">
-        <v>0</v>
-      </c>
-      <c r="D19" s="32">
+      <c r="C19" s="30">
+        <v>0</v>
+      </c>
+      <c r="D19" s="30">
         <v>10</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="30">
         <v>10</v>
       </c>
-      <c r="F19" s="32">
-        <v>0</v>
-      </c>
-      <c r="G19" s="32">
-        <v>0</v>
-      </c>
-      <c r="H19" s="32">
-        <v>0</v>
-      </c>
-      <c r="I19" s="33">
-        <f t="shared" si="14"/>
+      <c r="F19" s="30">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30">
+        <v>0</v>
+      </c>
+      <c r="H19" s="30">
+        <v>0</v>
+      </c>
+      <c r="I19" s="31">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="J19" s="1">
         <v>20</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="31" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B20" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="31">
         <f>SUM(C14:C19)</f>
         <v>10</v>
       </c>
-      <c r="D20" s="33">
-        <f t="shared" ref="D20:H20" si="15">SUM(D14:D19)</f>
+      <c r="D20" s="31">
+        <f t="shared" ref="D20:H20" si="1">SUM(D14:D19)</f>
         <v>10</v>
       </c>
-      <c r="E20" s="33">
-        <f t="shared" si="15"/>
+      <c r="E20" s="31">
+        <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="F20" s="33">
-        <f t="shared" si="15"/>
+      <c r="F20" s="31">
+        <f t="shared" si="1"/>
         <v>25</v>
       </c>
-      <c r="G20" s="33">
-        <f t="shared" si="15"/>
+      <c r="G20" s="31">
+        <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="H20" s="33">
-        <f t="shared" si="15"/>
+      <c r="H20" s="31">
+        <f t="shared" si="1"/>
         <v>10</v>
       </c>
       <c r="J20" s="1"/>
     </row>
-    <row r="21">
-      <c r="B21" s="30" t="s">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B21" s="28" t="s">
         <v>101</v>
       </c>
       <c r="C21" s="1">
@@ -4707,46 +4770,46 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="15"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B22" s="14"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="22">
         <f>SUMPRODUCT(C4:H9,C14:H19)</f>
         <v>375</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="4" t="s">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B28" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="J28" s="4" t="s">
+      <c r="D28" s="37"/>
+      <c r="E28" s="37"/>
+      <c r="F28" s="37"/>
+      <c r="J28" s="37" t="s">
         <v>91</v>
       </c>
-      <c r="K28" s="4" t="s">
+      <c r="K28" s="37" t="s">
         <v>92</v>
       </c>
-      <c r="L28" s="4"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="4"/>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="37"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="B29" s="37"/>
       <c r="C29" t="s">
         <v>118</v>
       </c>
@@ -4762,7 +4825,7 @@
       <c r="G29" t="s">
         <v>100</v>
       </c>
-      <c r="J29" s="4"/>
+      <c r="J29" s="37"/>
       <c r="K29" t="s">
         <v>118</v>
       </c>
@@ -4779,7 +4842,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
         <v>97</v>
       </c>
@@ -4814,14 +4877,14 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <f t="shared" ref="O30:O32" si="16">SUM(K30:N30)</f>
+        <f t="shared" ref="O30:O32" si="2">SUM(K30:N30)</f>
         <v>30</v>
       </c>
       <c r="P30">
         <v>30</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>98</v>
       </c>
@@ -4856,14 +4919,14 @@
         <v>20</v>
       </c>
       <c r="O31">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>50</v>
       </c>
       <c r="P31">
         <v>50</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>99</v>
       </c>
@@ -4898,14 +4961,14 @@
         <v>10</v>
       </c>
       <c r="O32">
-        <f t="shared" si="16"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="P32">
         <v>40</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>100</v>
       </c>
@@ -4926,19 +4989,19 @@
         <v>30</v>
       </c>
       <c r="L33">
-        <f t="shared" ref="L33:N33" si="17">SUM(L30:L32)</f>
+        <f t="shared" ref="L33:N33" si="3">SUM(L30:L32)</f>
         <v>20</v>
       </c>
       <c r="M33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>40</v>
       </c>
       <c r="N33">
-        <f t="shared" si="17"/>
+        <f t="shared" si="3"/>
         <v>30</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.25">
       <c r="J34" t="s">
         <v>100</v>
       </c>
@@ -4955,29 +5018,29 @@
         <v>30</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:14" x14ac:dyDescent="0.25">
       <c r="K36">
         <f>SUMPRODUCT(C30:F32,K30:N32)</f>
         <v>420</v>
       </c>
     </row>
-    <row r="38">
-      <c r="C38" s="24"/>
-      <c r="D38" s="24"/>
-      <c r="E38" s="24"/>
-      <c r="F38" s="24"/>
-    </row>
-    <row r="39">
-      <c r="C39" s="24"/>
-      <c r="D39" s="24"/>
-      <c r="E39" s="24"/>
-      <c r="F39" s="24"/>
-    </row>
-    <row r="40">
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
-      <c r="E40" s="24"/>
-      <c r="F40" s="24"/>
+    <row r="38" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="23"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -4992,27 +5055,26 @@
     <mergeCell ref="C12:G12"/>
     <mergeCell ref="J12:J13"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="14.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:Q17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="C1" s="4" t="s">
+    <row r="1" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="C1" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-    </row>
-    <row r="2">
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+    </row>
+    <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
         <v>123</v>
       </c>
@@ -5046,8 +5108,20 @@
       <c r="L2" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="M2" s="39" t="s">
+        <v>135</v>
+      </c>
+      <c r="N2" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q2" s="39" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B3" s="4">
         <v>1</v>
       </c>
@@ -5066,20 +5140,20 @@
       <c r="G3" s="4">
         <v>58</v>
       </c>
-      <c r="H3" s="34">
-        <f t="shared" ref="H3:H12" si="18">COUNT(C3:G3)</f>
+      <c r="H3" s="32">
+        <f t="shared" ref="H3:H12" si="0">COUNT(C3:G3)</f>
         <v>5</v>
       </c>
-      <c r="I3" s="35">
+      <c r="I3" s="33">
         <f>AVERAGE(C3:G3)</f>
-        <v>52.799999999999997</v>
+        <v>52.8</v>
       </c>
       <c r="J3">
         <f>MIN(C3:G3)</f>
         <v>43</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K12" si="19">MAX(C3:G3)</f>
+        <f>MAX(C3:G3)</f>
         <v>60</v>
       </c>
       <c r="L3">
@@ -5094,8 +5168,16 @@
         <f>L17</f>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="P3">
+        <f>0*$L$14</f>
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f>2.115*$L$14</f>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B4" s="4">
         <v>2</v>
       </c>
@@ -5114,36 +5196,44 @@
       <c r="G4" s="4">
         <v>66</v>
       </c>
-      <c r="H4" s="34">
-        <f t="shared" si="18"/>
+      <c r="H4" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I4" s="35">
-        <f t="shared" ref="I4:I12" si="20">AVERAGE(C4:G4)</f>
-        <v>58.399999999999999</v>
+      <c r="I4" s="33">
+        <f t="shared" ref="I4:I12" si="1">AVERAGE(C4:G4)</f>
+        <v>58.4</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J12" si="21">MIN(C4:G4)</f>
+        <f t="shared" ref="J4:J12" si="2">MIN(C4:G4)</f>
         <v>45</v>
       </c>
       <c r="K4">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="K3:K12" si="3">MAX(C4:G4)</f>
         <v>67</v>
       </c>
       <c r="L4">
-        <f t="shared" ref="L4:L12" si="22">K4-J4</f>
+        <f t="shared" ref="L4:L12" si="4">K4-J4</f>
         <v>22</v>
       </c>
       <c r="M4">
-        <f t="shared" ref="M4:M12" si="23">M3</f>
+        <f t="shared" ref="M4:M12" si="5">M3</f>
         <v>81.10560000000001</v>
       </c>
       <c r="N4">
-        <f t="shared" ref="N4:N12" si="24">N3</f>
+        <f t="shared" ref="N4:N12" si="6">N3</f>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="P4" s="9">
+        <f t="shared" ref="P4:P12" si="7">0*$L$14</f>
+        <v>0</v>
+      </c>
+      <c r="Q4" s="9">
+        <f t="shared" ref="Q4:Q12" si="8">2.115*$L$14</f>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B5" s="4">
         <v>3</v>
       </c>
@@ -5162,36 +5252,44 @@
       <c r="G5" s="4">
         <v>78</v>
       </c>
-      <c r="H5" s="34">
-        <f t="shared" si="18"/>
+      <c r="H5" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I5" s="35">
-        <f t="shared" si="20"/>
-        <v>61.399999999999999</v>
+      <c r="I5" s="33">
+        <f t="shared" si="1"/>
+        <v>61.4</v>
       </c>
       <c r="J5">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>40</v>
       </c>
       <c r="K5">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>78</v>
       </c>
       <c r="L5">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>38</v>
       </c>
       <c r="M5">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N5">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="6">
+      <c r="P5" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q5" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
         <v>4</v>
       </c>
@@ -5210,36 +5308,44 @@
       <c r="G6" s="4">
         <v>60</v>
       </c>
-      <c r="H6" s="34">
-        <f t="shared" si="18"/>
+      <c r="H6" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I6" s="35">
-        <f t="shared" si="20"/>
+      <c r="I6" s="33">
+        <f t="shared" si="1"/>
         <v>75</v>
       </c>
       <c r="J6">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="K6">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>89</v>
       </c>
       <c r="L6">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="M6">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N6">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="P6" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" s="4">
         <v>5</v>
       </c>
@@ -5258,36 +5364,44 @@
       <c r="G7" s="4">
         <v>70</v>
       </c>
-      <c r="H7" s="34">
-        <f t="shared" si="18"/>
+      <c r="H7" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I7" s="35">
-        <f t="shared" si="20"/>
-        <v>51.799999999999997</v>
+      <c r="I7" s="33">
+        <f t="shared" si="1"/>
+        <v>51.8</v>
       </c>
       <c r="J7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="K7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>70</v>
       </c>
       <c r="L7">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>32</v>
       </c>
       <c r="M7">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N7">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="8">
+      <c r="P7" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B8" s="4">
         <v>6</v>
       </c>
@@ -5306,36 +5420,44 @@
       <c r="G8" s="4">
         <v>80</v>
       </c>
-      <c r="H8" s="34">
-        <f t="shared" si="18"/>
+      <c r="H8" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I8" s="35">
-        <f t="shared" si="20"/>
-        <v>50.799999999999997</v>
+      <c r="I8" s="33">
+        <f t="shared" si="1"/>
+        <v>50.8</v>
       </c>
       <c r="J8">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="K8">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="L8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>51</v>
       </c>
       <c r="M8">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N8">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="P8" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B9" s="4">
         <v>7</v>
       </c>
@@ -5354,36 +5476,44 @@
       <c r="G9" s="4">
         <v>80</v>
       </c>
-      <c r="H9" s="34">
-        <f t="shared" si="18"/>
+      <c r="H9" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I9" s="35">
-        <f t="shared" si="20"/>
-        <v>60.799999999999997</v>
+      <c r="I9" s="33">
+        <f t="shared" si="1"/>
+        <v>60.8</v>
       </c>
       <c r="J9">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="K9">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>80</v>
       </c>
       <c r="L9">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>50</v>
       </c>
       <c r="M9">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N9">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="10">
+      <c r="P9" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B10" s="4">
         <v>8</v>
       </c>
@@ -5402,36 +5532,44 @@
       <c r="G10" s="4">
         <v>89</v>
       </c>
-      <c r="H10" s="34">
-        <f t="shared" si="18"/>
+      <c r="H10" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I10" s="35">
-        <f t="shared" si="20"/>
+      <c r="I10" s="33">
+        <f t="shared" si="1"/>
         <v>72.599999999999994</v>
       </c>
       <c r="J10">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>60</v>
       </c>
       <c r="K10">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>89</v>
       </c>
       <c r="L10">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="M10">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N10">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="P10" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="11" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
         <v>9</v>
       </c>
@@ -5450,36 +5588,44 @@
       <c r="G11" s="4">
         <v>79</v>
       </c>
-      <c r="H11" s="34">
-        <f t="shared" si="18"/>
+      <c r="H11" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I11" s="35">
-        <f t="shared" si="20"/>
-        <v>62.200000000000003</v>
+      <c r="I11" s="33">
+        <f t="shared" si="1"/>
+        <v>62.2</v>
       </c>
       <c r="J11">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>48</v>
       </c>
       <c r="K11">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>79</v>
       </c>
       <c r="L11">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="M11">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N11">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="12">
+      <c r="P11" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="12" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B12" s="4">
         <v>10</v>
       </c>
@@ -5498,37 +5644,45 @@
       <c r="G12" s="4">
         <v>84</v>
       </c>
-      <c r="H12" s="34">
-        <f t="shared" si="18"/>
+      <c r="H12" s="32">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="I12" s="35">
-        <f t="shared" si="20"/>
+      <c r="I12" s="33">
+        <f t="shared" si="1"/>
         <v>76</v>
       </c>
       <c r="J12">
-        <f t="shared" si="21"/>
+        <f t="shared" si="2"/>
         <v>56</v>
       </c>
       <c r="K12">
-        <f t="shared" si="19"/>
+        <f t="shared" si="3"/>
         <v>85</v>
       </c>
       <c r="L12">
-        <f t="shared" si="22"/>
+        <f t="shared" si="4"/>
         <v>29</v>
       </c>
       <c r="M12">
-        <f t="shared" si="23"/>
+        <f t="shared" si="5"/>
         <v>81.10560000000001</v>
       </c>
       <c r="N12">
-        <f t="shared" si="24"/>
+        <f t="shared" si="6"/>
         <v>43.254400000000011</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="I14" s="35">
+      <c r="P12" s="9">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <f t="shared" si="8"/>
+        <v>69.372</v>
+      </c>
+    </row>
+    <row r="14" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="I14" s="33">
         <f>AVERAGE(I3:I12)</f>
         <v>62.180000000000007</v>
       </c>
@@ -5537,7 +5691,15 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="16">
+    <row r="15" spans="2:17" x14ac:dyDescent="0.25">
+      <c r="O15" s="39" t="s">
+        <v>130</v>
+      </c>
+      <c r="P15" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="2:17" x14ac:dyDescent="0.25">
       <c r="K16" t="s">
         <v>128</v>
       </c>
@@ -5545,8 +5707,17 @@
         <f>I14+0.577*L14</f>
         <v>81.10560000000001</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="O16" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="P16" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q16" s="39" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.25">
       <c r="K17" t="s">
         <v>129</v>
       </c>
@@ -5559,10 +5730,8 @@
   <mergeCells count="1">
     <mergeCell ref="C1:G1"/>
   </mergeCells>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.69999999999999996" right="0.69999999999999996" top="0.75" bottom="0.75" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>